--- a/Property Details.-EM.xlsx
+++ b/Property Details.-EM.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ABKR\Real Estate-Trans\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDB828A-A5A3-4C28-84D1-E349B0AF553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Property Master" sheetId="1" r:id="rId1"/>
@@ -22,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Unit Master'!$A$1:$AJ$178</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="476">
   <si>
     <t>Cost Center Name</t>
   </si>
@@ -1450,18 +1444,36 @@
   </si>
   <si>
     <t>Customer(PDC)-AAA Flat16</t>
+  </si>
+  <si>
+    <t>Double Toned</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Toned</t>
+  </si>
+  <si>
+    <t>Wheel</t>
+  </si>
+  <si>
+    <t>Dettol Kitchen</t>
+  </si>
+  <si>
+    <t>Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1695,7 +1707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1808,7 +1820,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1857,6 +1869,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="16" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2023,7 +2038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG486"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
@@ -20671,43 +20686,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$B$2:$B$12</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$C$2:$C$7</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000003000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$E$2:$E$9</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000004000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$H$2:$H$33</xm:f>
           </x14:formula1>
           <xm:sqref>W2:AA486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000005000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$D$2:$D$8</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE486</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000006000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$G$2:$G$5</xm:f>
           </x14:formula1>
@@ -20720,7 +20735,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ178"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
@@ -32927,85 +32942,85 @@
       <c r="AJ178" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ178" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:AJ178"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000001000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$S$2:$S$6</xm:f>
           </x14:formula1>
           <xm:sqref>AG2:AG178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000002000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$G$2:$G$5</xm:f>
           </x14:formula1>
           <xm:sqref>AI51:AI66 AI3:AI48 AI68:AI178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$W$2:$W$4</xm:f>
           </x14:formula1>
           <xm:sqref>AD1 AD15:AD20 AD37 AD41:AD48 AD13 AD5:AD10 AD27:AD35 AD22:AD25 AD51:AD66 AD68:AD1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000000000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$R$2:$R$7</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000004000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$I$2:$I$14</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000005000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$J$2:$J$10</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000006000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$K$2:$K$8</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000007000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$L$2:$L$8</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000008000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$N$2:$N$9</xm:f>
           </x14:formula1>
           <xm:sqref>O2:O178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000009000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$O$2:$O$5</xm:f>
           </x14:formula1>
           <xm:sqref>P2:P178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$P$2:$P$8</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Dropdown Lists'!$Q$2:$Q$8</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V178</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+        <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>'Property Master'!$A$2:$A$486</xm:f>
           </x14:formula1>
@@ -33018,7 +33033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15"/>
   <cols>
@@ -34291,8 +34306,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9B9061-9275-4D62-8084-A2E7D0DF169A}">
-  <dimension ref="A2:F104"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:K104"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.875" style="58" customWidth="1"/>
@@ -34709,7 +34724,7 @@
       <c r="B59" s="38" t="s">
         <v>454</v>
       </c>
-      <c r="C59" s="40" t="s">
+      <c r="C59" s="75" t="s">
         <v>469</v>
       </c>
       <c r="D59" s="41"/>
@@ -34751,7 +34766,7 @@
       <c r="B63" s="38" t="s">
         <v>454</v>
       </c>
-      <c r="C63" s="40" t="s">
+      <c r="C63" s="75" t="s">
         <v>457</v>
       </c>
       <c r="D63" s="57"/>
@@ -34765,7 +34780,7 @@
       <c r="D64" s="51"/>
       <c r="E64" s="51"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:11">
       <c r="A65" s="39">
         <v>2</v>
       </c>
@@ -34776,7 +34791,7 @@
       <c r="D65" s="51"/>
       <c r="E65" s="51"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:11">
       <c r="B66" s="38" t="s">
         <v>453</v>
       </c>
@@ -34788,7 +34803,7 @@
       </c>
       <c r="E66" s="51"/>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:11">
       <c r="B67" s="38" t="s">
         <v>454</v>
       </c>
@@ -34801,12 +34816,12 @@
       </c>
       <c r="F67" s="57"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:11">
       <c r="C68" s="51"/>
       <c r="D68" s="51"/>
       <c r="E68" s="51"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:11">
       <c r="A69" s="38">
         <v>2.1</v>
       </c>
@@ -34821,11 +34836,11 @@
       </c>
       <c r="E69" s="51"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:11">
       <c r="B70" s="38" t="s">
         <v>454</v>
       </c>
-      <c r="C70" s="40" t="s">
+      <c r="C70" s="75" t="s">
         <v>459</v>
       </c>
       <c r="D70" s="57"/>
@@ -34833,12 +34848,12 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:11">
       <c r="C71" s="51"/>
       <c r="D71" s="51"/>
       <c r="E71" s="51"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:11">
       <c r="B72" s="34" t="s">
         <v>461</v>
       </c>
@@ -34846,7 +34861,7 @@
       <c r="D72" s="51"/>
       <c r="E72" s="51"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:11">
       <c r="B73" s="38" t="s">
         <v>453</v>
       </c>
@@ -34858,7 +34873,7 @@
       </c>
       <c r="E73" s="51"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:11">
       <c r="B74" s="38" t="s">
         <v>454</v>
       </c>
@@ -34870,12 +34885,18 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:11">
       <c r="C75" s="51"/>
       <c r="D75" s="51"/>
       <c r="E75" s="51"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="I75" t="s">
+        <v>470</v>
+      </c>
+      <c r="K75" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="49">
         <v>3</v>
       </c>
@@ -34885,8 +34906,14 @@
       <c r="C76" s="51"/>
       <c r="D76" s="51"/>
       <c r="E76" s="51"/>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="I76" t="s">
+        <v>472</v>
+      </c>
+      <c r="K76" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="52"/>
       <c r="B77" s="53" t="s">
         <v>453</v>
@@ -34898,8 +34925,14 @@
         <v>5600</v>
       </c>
       <c r="E77" s="51"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="I77" t="s">
+        <v>473</v>
+      </c>
+      <c r="K77" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="52"/>
       <c r="B78" s="53" t="s">
         <v>454</v>
@@ -34911,15 +34944,27 @@
       <c r="E78" s="55">
         <v>5600</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="I78" t="s">
+        <v>474</v>
+      </c>
+      <c r="J78">
+        <v>179</v>
+      </c>
+      <c r="K78" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="52"/>
       <c r="B79" s="51"/>
       <c r="C79" s="51"/>
       <c r="D79" s="51"/>
       <c r="E79" s="51"/>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="K79" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="52"/>
       <c r="B80" s="53" t="s">
         <v>453</v>
@@ -35066,7 +35111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D909FC8-F51B-4F87-86E8-B300F27B7F13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>

--- a/Property Details.-EM.xlsx
+++ b/Property Details.-EM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Property Master" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="479">
   <si>
     <t>Cost Center Name</t>
   </si>
@@ -1446,22 +1446,31 @@
     <t>Customer(PDC)-AAA Flat16</t>
   </si>
   <si>
-    <t>Double Toned</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Toned</t>
-  </si>
-  <si>
-    <t>Wheel</t>
-  </si>
-  <si>
-    <t>Dettol Kitchen</t>
-  </si>
-  <si>
-    <t>Z</t>
+    <t>Debit</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>PDC in hand</t>
+  </si>
+  <si>
+    <t>Bank Account</t>
+  </si>
+  <si>
+    <t>Settlement</t>
+  </si>
+  <si>
+    <t>Cash/ bank</t>
+  </si>
+  <si>
+    <t>Cash In Hand/ Bank</t>
+  </si>
+  <si>
+    <t>Payment to Customer</t>
+  </si>
+  <si>
+    <t>Credirt</t>
   </si>
 </sst>
 </file>
@@ -34307,7 +34316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K104"/>
+  <dimension ref="A2:F125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.875" style="58" customWidth="1"/>
@@ -34780,7 +34789,7 @@
       <c r="D64" s="51"/>
       <c r="E64" s="51"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:6">
       <c r="A65" s="39">
         <v>2</v>
       </c>
@@ -34791,7 +34800,7 @@
       <c r="D65" s="51"/>
       <c r="E65" s="51"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:6">
       <c r="B66" s="38" t="s">
         <v>453</v>
       </c>
@@ -34803,7 +34812,7 @@
       </c>
       <c r="E66" s="51"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:6">
       <c r="B67" s="38" t="s">
         <v>454</v>
       </c>
@@ -34816,12 +34825,12 @@
       </c>
       <c r="F67" s="57"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:6">
       <c r="C68" s="51"/>
       <c r="D68" s="51"/>
       <c r="E68" s="51"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:6">
       <c r="A69" s="38">
         <v>2.1</v>
       </c>
@@ -34836,7 +34845,7 @@
       </c>
       <c r="E69" s="51"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:6">
       <c r="B70" s="38" t="s">
         <v>454</v>
       </c>
@@ -34848,12 +34857,12 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:6">
       <c r="C71" s="51"/>
       <c r="D71" s="51"/>
       <c r="E71" s="51"/>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:6">
       <c r="B72" s="34" t="s">
         <v>461</v>
       </c>
@@ -34861,7 +34870,7 @@
       <c r="D72" s="51"/>
       <c r="E72" s="51"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:6">
       <c r="B73" s="38" t="s">
         <v>453</v>
       </c>
@@ -34873,7 +34882,7 @@
       </c>
       <c r="E73" s="51"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:6">
       <c r="B74" s="38" t="s">
         <v>454</v>
       </c>
@@ -34885,18 +34894,12 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:6">
       <c r="C75" s="51"/>
       <c r="D75" s="51"/>
       <c r="E75" s="51"/>
-      <c r="I75" t="s">
-        <v>470</v>
-      </c>
-      <c r="K75" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="49">
         <v>3</v>
       </c>
@@ -34906,14 +34909,8 @@
       <c r="C76" s="51"/>
       <c r="D76" s="51"/>
       <c r="E76" s="51"/>
-      <c r="I76" t="s">
-        <v>472</v>
-      </c>
-      <c r="K76" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="52"/>
       <c r="B77" s="53" t="s">
         <v>453</v>
@@ -34925,14 +34922,8 @@
         <v>5600</v>
       </c>
       <c r="E77" s="51"/>
-      <c r="I77" t="s">
-        <v>473</v>
-      </c>
-      <c r="K77" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="52"/>
       <c r="B78" s="53" t="s">
         <v>454</v>
@@ -34944,27 +34935,15 @@
       <c r="E78" s="55">
         <v>5600</v>
       </c>
-      <c r="I78" t="s">
-        <v>474</v>
-      </c>
-      <c r="J78">
-        <v>179</v>
-      </c>
-      <c r="K78" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="52"/>
       <c r="B79" s="51"/>
       <c r="C79" s="51"/>
       <c r="D79" s="51"/>
       <c r="E79" s="51"/>
-      <c r="K79" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="52"/>
       <c r="B80" s="53" t="s">
         <v>453</v>
@@ -35090,20 +35069,135 @@
       <c r="E100" s="41"/>
     </row>
     <row r="101" spans="2:5">
-      <c r="C101" s="38"/>
+      <c r="B101" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="C101" t="s">
+        <v>470</v>
+      </c>
       <c r="E101" s="41"/>
     </row>
     <row r="102" spans="2:5">
-      <c r="B102" s="38"/>
+      <c r="B102" s="54" t="s">
+        <v>459</v>
+      </c>
+      <c r="C102" t="s">
+        <v>471</v>
+      </c>
       <c r="D102" s="45"/>
       <c r="E102" s="45"/>
     </row>
-    <row r="103" spans="2:5">
-      <c r="B103" s="38"/>
-    </row>
     <row r="104" spans="2:5">
-      <c r="C104" s="40"/>
+      <c r="B104" s="54" t="s">
+        <v>469</v>
+      </c>
+      <c r="C104" t="s">
+        <v>470</v>
+      </c>
       <c r="E104" s="43"/>
+    </row>
+    <row r="105" spans="2:5">
+      <c r="B105" s="57" t="s">
+        <v>472</v>
+      </c>
+      <c r="C105" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5">
+      <c r="B107" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="C107" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="B108" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="C108" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5">
+      <c r="B112" s="57" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113" s="57">
+        <v>12100</v>
+      </c>
+      <c r="C113" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114" s="57">
+        <v>12413</v>
+      </c>
+      <c r="C114" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="B115" s="57" t="s">
+        <v>476</v>
+      </c>
+      <c r="C115" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="B117" s="57" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="B118" s="57">
+        <v>21500</v>
+      </c>
+      <c r="C118" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="B119" s="57">
+        <v>12100</v>
+      </c>
+      <c r="C119" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="B120" s="57">
+        <v>12413</v>
+      </c>
+      <c r="C120" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="B122" s="57" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="B124" s="57">
+        <v>21500</v>
+      </c>
+      <c r="C124" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="B125" s="57" t="s">
+        <v>476</v>
+      </c>
+      <c r="C125" t="s">
+        <v>478</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
